--- a/docs/alliance-import-templates/05-专家资源导入模板-mock数据.xlsx
+++ b/docs/alliance-import-templates/05-专家资源导入模板-mock数据.xlsx
@@ -10,20 +10,24 @@
     <sheet name="专家资源" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'专家资源'!$A$2:$H$2</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'专家资源'!$A$2:$K$2</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>填写说明：
 * 必填列。
 头衔 / 职位 / 行业 / 城市：文本，选填
 简介：文本，选填
-【关联参考列】（青蓝色表头，导入时忽略）：关联企业 / 擅长领域 为跨表单 mock 数据关联，多值用中文分号「；」分隔，需与对应导入模板中的名称保持一致</t>
+年龄：数字，选填
+从业年限：数字（年），选填
+关联合作企业：企业名称，选填，按名称匹配导入
+擅长领域：文本，选填，多值用中文分号「；」分隔
+从业经历：文本，选填</t>
   </si>
   <si>
     <t>姓名 *</t>
@@ -44,12 +48,21 @@
     <t>简介</t>
   </si>
   <si>
-    <t>关联企业名称</t>
+    <t>年龄</t>
+  </si>
+  <si>
+    <t>从业年限</t>
+  </si>
+  <si>
+    <t>关联合作企业</t>
   </si>
   <si>
     <t>擅长领域</t>
   </si>
   <si>
+    <t>从业经历</t>
+  </si>
+  <si>
     <t>王建军</t>
   </si>
   <si>
@@ -68,12 +81,21 @@
     <t>工业机器人与机器视觉领域专家，主持多项省部级科研课题</t>
   </si>
   <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>苏州华芯智能制造有限公司</t>
   </si>
   <si>
     <t>机器视觉；工业机器人</t>
   </si>
   <si>
+    <t>历任华芯智能总工程师，主持视觉质检系统核心算法研发，累计培养工程硕士 30 余名</t>
+  </si>
+  <si>
     <t>李敏</t>
   </si>
   <si>
@@ -92,12 +114,21 @@
     <t>新能源汽车电控系统研发专家，参与多项企业技术改造项目</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>南京云驰新能源科技有限公司</t>
   </si>
   <si>
     <t>电控系统；高压安全</t>
   </si>
   <si>
+    <t>云驰新能源电控平台负责人，主导高压安全实训课程体系开发</t>
+  </si>
+  <si>
     <t>陈晓东</t>
   </si>
   <si>
@@ -116,12 +147,21 @@
     <t>职业教育装备规划专家，长期从事产教融合实训基地建设研究</t>
   </si>
   <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>无锡智联教育装备有限公司</t>
   </si>
   <si>
     <t>实训装备；专业群建设</t>
   </si>
   <si>
+    <t>主持省部级产教融合课题 8 项，参与多所院校实训基地规划</t>
+  </si>
+  <si>
     <t>周晓芳</t>
   </si>
   <si>
@@ -140,17 +180,26 @@
     <t>生物医药质量管理专家，参与校企协同育人项目设计与实施</t>
   </si>
   <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>常州康健生物医药有限公司</t>
   </si>
   <si>
     <t>药品质量管理；现代学徒制</t>
+  </si>
+  <si>
+    <t>康健生物质量总监，主导 GMP 质量管理体系建设与学徒制带教</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -167,13 +216,8 @@
       <color rgb="FF595959"/>
       <sz val="10"/>
     </font>
-    <font>
-      <family val="2"/>
-      <color rgb="FF2E74B5"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,6 +227,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E74B5"/>
       </patternFill>
     </fill>
     <fill>
@@ -208,10 +257,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -489,21 +538,26 @@
     <col customWidth="true" max="4" min="4" width="20"/>
     <col customWidth="true" max="5" min="5" width="18"/>
     <col customWidth="true" max="6" min="6" width="48"/>
-    <col customWidth="true" max="7" min="7" width="32"/>
-    <col customWidth="true" max="8" min="8" width="36"/>
+    <col customWidth="true" max="7" min="7" width="12"/>
+    <col customWidth="true" max="8" min="8" width="14"/>
+    <col customWidth="true" max="10" min="9" width="40"/>
+    <col customWidth="true" max="11" min="11" width="48"/>
   </cols>
   <sheetData>
     <row r="1" ht="105" customHeight="true">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
     </row>
     <row r="2" ht="26" customHeight="true">
       <c r="A2" s="1" t="s">
@@ -524,121 +578,166 @@
       <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="true">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="true">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="true">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="true">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="G6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$2:$H$2"/>
+  <autoFilter ref="$A$2:$K$2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
 </worksheet>
 </file>